--- a/docs/应用使能 6.0.0 通信矩阵.xlsx
+++ b/docs/应用使能 6.0.0 通信矩阵.xlsx
@@ -1,16 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17055" tabRatio="530"/>
+    <workbookView windowWidth="27945" windowHeight="11655" tabRatio="530" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="MindSDK" sheetId="9" r:id="rId1"/>
+    <sheet name="RecSDK-Torch" sheetId="10" r:id="rId2"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId6"/>
+    <externalReference r:id="rId7"/>
   </externalReferences>
   <definedNames>
     <definedName name="_FTN1">#REF!</definedName>
@@ -449,8 +450,424 @@
 </comments>
 </file>
 
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Administrator</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:
+IT Division:
+描述项解释
+源设备名称。
+写作要求
+1、注意大小写。例如NodeB
+举例
+1、M2000 Server
+2、NodeB</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:
+描述项解释
+源设备IP
+写作要求
+填写源设备端哪里的IP，该内容能够指导用户转换为所配置的具体IP地址。IP命名方式请遵循产品自身IP规划名称。
+举例
+1、OMU单板IP
+2、Console Client PC IP</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">Administrator:
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>描述项解释
+源端端口号或者端口范围。
+写作要求
+1、知名协议需要使用业界通用的端口
+2、源设备所开放的具体端口号，如存在多个端口号，则连续的情况下，直接以10000～10006的形式表述；非连续端口的情况，则以半角逗号间隔列举，如31280, 31780
+3、如果一个端口供SSL加密使用，一个端口给不加密情况使用，建议直接在具体端口号后面以半角括号说明如123(SSL), 125，同时在端口说明中具体描述。
+4、不确定的非侦听端口可以填写中文“随机端口”、“任意端口”等字样。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+描述项解释
+目的设备名称。
+写作要求
+1、注意大小写。例如NodeB
+2、对于本机内部的通讯端口，设备名称可以写为Localhost
+举例
+1、M2000 Server
+2、NodeB</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+描述项解释
+目的设备IP
+写作要求
+填写目的设备端哪里的IP，该内容能够指导用户转换为所配置的具体IP地址。IP命名方式请遵循产品自身IP规划名称。
+举例
+1、OMU单板IP
+2、Console Client PC IP</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+描述项解释
+目的端端口号或者端口范围，主要指提供服务的侦听端口。
+写作要求
+1、知名协议需要使用业界通用的端口
+2、目的设备所开放的具体端口号，如存在多个端口号，则连续的情况下，直接以10000～10006的形式表述；非连续端口的情况，则以半角逗号间隔列举，如31280, 31780
+3、如果一个端口供SSL加密使用，一个端口给不加密情况使用，建议直接在具体端口号后面以半角括号说明如123(SSL), 125，同时在端口说明中具体描述</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+描述项解释
+使用的协议类型，主要是传输层协议，TCP、UDP、SCTP等。
+下拉框选项并未限制输入，如果不能满足要求，且确有需求，可以自行填写。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+描述项解释
+侦听端口提供的服务详细描述。
+写作要求
+涉及的缩略语应在对应括号内提供中英文全名。
+必填：用于xxx功能。需写完整，可以参考样例页签。例如，对于M2000代理LMT的情况，不能只写用于网元LMT，而应写明用于M2000代理LMT等。
+对于使用的应用层非私有协议的端口还需填写：使用的应用层协议。
+(可选)，部署位置：对于非物理实体，需要写明通常的部署位置，如对于Web浏览器，应写明通常部署在客户端上，在使用Citrix方案时，则通常部署在Citrix客户端上。
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+描述项解释
+侦听端口是否可以通过软件配置界面或命令行进行更改。从整个网络层面来看，如果目的端口所在设备为其他设备，非本设备，则为不涉及。
+写作要求
+中文填写“是”或者“否”，
+英文填写“Yes”或者“No”。
+非侦听端口或目的端口非本设备，中文填写“不涉及”，英文填写“N/A”。
+举例
+如设备提供SSH服务，端口为22，通过软件管理界面是否可以改为其他端口如5000。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+与侦听端口通讯采用的认证方式，如用户名/密码、IP认证、证书认证等。
+1、如果该端口不需要进行认证就可以建立连接通讯，则中文填写“无”，英文填写“None”。也可统一中文填写“不涉及”，英文填写“N/A”
+* 所有能对系统进行管理的人机接口以及跨信任网络的机机接口必须具备认证机制。详情可以参考红线解读。
+2、如果标准协议不支持认证，则中文填写“不涉及”，英文填写“N/A”
+3、对于客户端端口，认证方式可写目的端口的认证方式。
+4、若一个端口存在2种或2种以上认证方式，请编辑表格填写，必须将各种认证方式填写全面。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+描述项解释
+与侦听端口通讯采用的加密方式。如SSL、SSH、HTTPS、TLS等。如涉及具体加密协议版本，需注明。
+1、如不进行加密，则中文填写“无”，英文填写“None”。
+* 敏感数据如需通过非信任网络传输，产品应支持安全传输通道或者将数据加密后再传输的机制。
+2、如标准协议不支持加密，则中文填写“不涉及”，英文填写“N/A”。
+3、若一个端口存在2种或2种以上传输内容加密方式，必须将各种加密方式填写全面。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="L1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+描述项解释
+描述侦听端口所属哪个平面，如用于OM面/管理面/维护面的端口、用于控制/信令面的端口、用于用户/业务面的端口、三个面共用的端口等。
+关于各个平面的定义请参考X.805标准。
+特殊情况：
+1、应根据实际情况填写，例如客户定制备份通道独立三面的情况，应增加填写备份面。
+2、应根据实际填写的平面更改“前言”页签中所属平面的说明，但是不允许出现相同面不同名情况，例如同时出现OM面和管理面。
+3、若一个端口存在2种或2种以上所属平面，必须将各种情况填写全面。
+4、所属平面主要针对电信设备而言，如果产品不涉及平面，可以删除该列。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+描述项解释
+侦听端口所对应目的设备的版本信息，写到C版本为止，即VxxxRyyyCzz。从整个网络层面来看，如果目的端口所在设备为其他设备，非本设备，则为不涉及。
+• 对于只适用于个别版本的端口，直接写版本号。
+• 对于基础版本引入的，即所有版本通用的，写成所有版本。
+• 对于从某个版本才引入的，写明xx版本及之后版本。
+• 对于基础版本引入，但到某具体版本删除了的，写明xx版本之前的版本（不包括xx版本在内）。
+• 对于定制版本，应该写明所属定制版本。
+• 其他特殊情况（如从某个版本引入，只有又在哪个版本删除的，按实际情况给出具体描述说明。）</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+描述项解释
+侦听端口应用的特殊场景。
+写作要求
+在不涉及的情况下，中文填写“无“，英文填写“None”。
+涉及的缩略语应在对应括号内提供中英文全名。
+包括但不限于以下特殊场景（均为可选，有则写，没有就不写）
+特殊组网：如异地双机、PRS和M2000共部署等情况，写明具体场景下的具体端口情况。
+端口为多选一：说明选择条件，即什么情况下应选择什么端口等。不涉及不写。
+应用网元限制：即使用该端口进行连接的网元。
+操作系统限制：即仅用于什么操作系统，如仅用于Solaris等</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="O1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="Tahoma"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="Tahoma"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>可以根据业务或客户需求自行定制内容，例如兼容老版本使用的情况。如无内容备注，可以删除该列。</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="64">
   <si>
     <t>源设备</t>
   </si>
@@ -624,6 +1041,30 @@
   </si>
   <si>
     <t>【作用】负责完成进程间的协调和管理工作</t>
+  </si>
+  <si>
+    <t>PyTorch的主节点（默认为Rank0所在节点）</t>
+  </si>
+  <si>
+    <t>PyTorch的主节点的IP地址，通过环境变量MASTER_ADDR配置</t>
+  </si>
+  <si>
+    <t>PyTorch侦听端口，通过环境变量MASTER_PORT进行配置，例如6000</t>
+  </si>
+  <si>
+    <t>随机端口，由操作系统自动分配，默认范围[32768,60999]</t>
+  </si>
+  <si>
+    <t>分布式训练进程间通信</t>
+  </si>
+  <si>
+    <t>无（延用PyTorch开源框架能力）</t>
+  </si>
+  <si>
+    <t>业务面</t>
+  </si>
+  <si>
+    <t>所有版本</t>
   </si>
 </sst>
 </file>
@@ -636,7 +1077,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="33">
+  <fonts count="30">
     <font>
       <sz val="11"/>
       <name val="宋体"/>
@@ -659,22 +1100,6 @@
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="major"/>
-    </font>
-    <font>
-      <sz val="10.5"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10.5"/>
-      <name val="宋体"/>
-      <charset val="134"/>
     </font>
     <font>
       <sz val="10.5"/>
@@ -849,12 +1274,12 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="Tahoma"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="Tahoma"/>
       <charset val="134"/>
@@ -1198,19 +1623,31 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1219,162 +1656,150 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1390,19 +1815,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1474,6 +1893,13 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/customStorage/customStorage.xml><?xml version="1.0" encoding="utf-8"?>
+<customStorage xmlns="https://web.wps.cn/et/2018/main">
+  <book/>
+  <sheets/>
+</customStorage>
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1799,15 +2225,15 @@
   <cols>
     <col min="1" max="1" width="38.75" customWidth="1"/>
     <col min="2" max="2" width="31.125" customWidth="1"/>
-    <col min="3" max="3" width="21.5" style="1" customWidth="1"/>
-    <col min="4" max="4" width="33.5" style="1" customWidth="1"/>
-    <col min="5" max="5" width="34.75" style="1" customWidth="1"/>
+    <col min="3" max="3" width="21.5" style="2" customWidth="1"/>
+    <col min="4" max="4" width="33.5" style="2" customWidth="1"/>
+    <col min="5" max="5" width="34.75" style="2" customWidth="1"/>
     <col min="6" max="6" width="25.5" customWidth="1"/>
-    <col min="7" max="7" width="23.125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="23.125" style="2" customWidth="1"/>
     <col min="8" max="8" width="37.625" customWidth="1"/>
-    <col min="9" max="9" width="10" style="1" customWidth="1"/>
+    <col min="9" max="9" width="10" style="2" customWidth="1"/>
     <col min="10" max="10" width="8" customWidth="1"/>
-    <col min="11" max="11" width="8.125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="8.125" style="2" customWidth="1"/>
     <col min="12" max="12" width="10" customWidth="1"/>
     <col min="13" max="13" width="8.75" customWidth="1"/>
     <col min="14" max="14" width="10.25" customWidth="1"/>
@@ -1815,49 +2241,49 @@
   </cols>
   <sheetData>
     <row r="1" ht="25.5" spans="1:15">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1889,22 +2315,22 @@
       <c r="I2" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="J2" s="11" t="s">
+      <c r="J2" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="K2" s="11" t="s">
+      <c r="K2" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="L2" s="11" t="s">
+      <c r="L2" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="M2" s="12" t="s">
+      <c r="M2" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="N2" s="11" t="s">
+      <c r="N2" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="O2" s="11" t="s">
+      <c r="O2" s="10" t="s">
         <v>27</v>
       </c>
     </row>
@@ -1936,22 +2362,22 @@
       <c r="I3" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="J3" s="11" t="s">
+      <c r="J3" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="K3" s="11" t="s">
+      <c r="K3" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="L3" s="11" t="s">
+      <c r="L3" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="M3" s="12" t="s">
+      <c r="M3" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="N3" s="11" t="s">
+      <c r="N3" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="O3" s="11" t="s">
+      <c r="O3" s="10" t="s">
         <v>27</v>
       </c>
     </row>
@@ -1983,22 +2409,22 @@
       <c r="I4" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="J4" s="11" t="s">
+      <c r="J4" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="K4" s="11" t="s">
+      <c r="K4" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="L4" s="11" t="s">
+      <c r="L4" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="M4" s="12" t="s">
+      <c r="M4" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="N4" s="11" t="s">
+      <c r="N4" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="O4" s="11" t="s">
+      <c r="O4" s="10" t="s">
         <v>26</v>
       </c>
     </row>
@@ -2030,22 +2456,22 @@
       <c r="I5" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="J5" s="11" t="s">
+      <c r="J5" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="K5" s="11" t="s">
+      <c r="K5" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="L5" s="11" t="s">
+      <c r="L5" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="M5" s="12" t="s">
+      <c r="M5" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="N5" s="11" t="s">
+      <c r="N5" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="O5" s="11" t="s">
+      <c r="O5" s="10" t="s">
         <v>26</v>
       </c>
     </row>
@@ -2077,22 +2503,22 @@
       <c r="I6" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="J6" s="11" t="s">
+      <c r="J6" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="K6" s="11" t="s">
+      <c r="K6" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="L6" s="11" t="s">
+      <c r="L6" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="M6" s="12" t="s">
+      <c r="M6" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="N6" s="11" t="s">
+      <c r="N6" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="O6" s="11" t="s">
+      <c r="O6" s="10" t="s">
         <v>26</v>
       </c>
     </row>
@@ -2124,22 +2550,22 @@
       <c r="I7" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="J7" s="11" t="s">
+      <c r="J7" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="K7" s="11" t="s">
+      <c r="K7" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="L7" s="11" t="s">
+      <c r="L7" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="M7" s="12" t="s">
+      <c r="M7" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="N7" s="11" t="s">
+      <c r="N7" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="O7" s="11" t="s">
+      <c r="O7" s="10" t="s">
         <v>26</v>
       </c>
     </row>
@@ -2180,13 +2606,13 @@
       <c r="L8" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="M8" s="12" t="s">
+      <c r="M8" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="N8" s="11" t="s">
+      <c r="N8" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="O8" s="11" t="s">
+      <c r="O8" s="10" t="s">
         <v>26</v>
       </c>
     </row>
@@ -2194,46 +2620,46 @@
       <c r="A9" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="C9" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="D9" s="10" t="s">
+      <c r="D9" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="E9" s="10" t="s">
+      <c r="E9" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="F9" s="10" t="s">
+      <c r="F9" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="G9" s="10" t="s">
+      <c r="G9" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="H9" s="9" t="s">
+      <c r="H9" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="I9" s="10" t="s">
+      <c r="I9" s="9" t="s">
         <v>52</v>
       </c>
       <c r="J9" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="K9" s="10" t="s">
+      <c r="K9" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="L9" s="11" t="s">
+      <c r="L9" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="M9" s="12" t="s">
+      <c r="M9" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="N9" s="11" t="s">
+      <c r="N9" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="O9" s="12" t="s">
+      <c r="O9" s="10" t="s">
         <v>26</v>
       </c>
     </row>
@@ -2241,46 +2667,46 @@
       <c r="A10" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="C10" s="10" t="s">
+      <c r="C10" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="D10" s="10" t="s">
+      <c r="D10" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="E10" s="10" t="s">
+      <c r="E10" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="F10" s="9" t="s">
+      <c r="F10" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="G10" s="10" t="s">
+      <c r="G10" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="H10" s="9" t="s">
+      <c r="H10" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="I10" s="10" t="s">
+      <c r="I10" s="9" t="s">
         <v>21</v>
       </c>
       <c r="J10" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="K10" s="10" t="s">
+      <c r="K10" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="L10" s="11" t="s">
+      <c r="L10" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="M10" s="12" t="s">
+      <c r="M10" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="N10" s="11" t="s">
+      <c r="N10" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="O10" s="12" t="s">
+      <c r="O10" s="10" t="s">
         <v>54</v>
       </c>
     </row>
@@ -2288,46 +2714,46 @@
       <c r="A11" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="C11" s="10" t="s">
+      <c r="C11" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="D11" s="10" t="s">
+      <c r="D11" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="E11" s="10" t="s">
+      <c r="E11" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="F11" s="10" t="s">
+      <c r="F11" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="G11" s="10" t="s">
+      <c r="G11" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="H11" s="9" t="s">
+      <c r="H11" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="I11" s="10" t="s">
+      <c r="I11" s="9" t="s">
         <v>52</v>
       </c>
       <c r="J11" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="K11" s="10" t="s">
+      <c r="K11" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="L11" s="11" t="s">
+      <c r="L11" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="M11" s="12" t="s">
+      <c r="M11" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="N11" s="11" t="s">
+      <c r="N11" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="O11" s="12" t="s">
+      <c r="O11" s="10" t="s">
         <v>54</v>
       </c>
     </row>
@@ -2343,6 +2769,161 @@
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:O3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2"/>
+  <cols>
+    <col min="1" max="1" width="24.125" customWidth="1"/>
+    <col min="2" max="2" width="25.625" customWidth="1"/>
+    <col min="3" max="3" width="18.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="38.25" spans="1:15">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E2" t="s">
+        <v>57</v>
+      </c>
+      <c r="F2" t="s">
+        <v>59</v>
+      </c>
+      <c r="G2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H2" t="s">
+        <v>60</v>
+      </c>
+      <c r="I2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J2" t="s">
+        <v>61</v>
+      </c>
+      <c r="K2" t="s">
+        <v>61</v>
+      </c>
+      <c r="L2" t="s">
+        <v>62</v>
+      </c>
+      <c r="M2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F3" t="s">
+        <v>58</v>
+      </c>
+      <c r="G3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s">
+        <v>60</v>
+      </c>
+      <c r="I3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J3" t="s">
+        <v>61</v>
+      </c>
+      <c r="K3" t="s">
+        <v>61</v>
+      </c>
+      <c r="L3" t="s">
+        <v>62</v>
+      </c>
+      <c r="M3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="G1">
+      <formula1>"TCP,UDP,SCTP,TCPv6,UDPv6"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="I1">
+      <formula1>" 是,否,不涉及"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
